--- a/data/piano_alimentare.xlsx
+++ b/data/piano_alimentare.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Piano Settimanale" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Giovanni - Ricette" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Rosalia - Piano 21gg" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Rosalia - Ricette" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Ricette da provare" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Lista della Spesa" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Piano Settimanale" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Giovanni - Ricette" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Rosalia - Piano 21gg" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Rosalia - Ricette" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Ricette da provare" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Lista della Spesa" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="457">
   <si>
     <t xml:space="preserve">PIANO ALIMENTARE SETTIMANALE — GIOVANNI · ~1700 kcal/giorno · 4 pasti</t>
   </si>
@@ -573,9 +573,18 @@
     <t xml:space="preserve">Tacos al manzo (chili leggero)</t>
   </si>
   <si>
+    <t xml:space="preserve">Merluzzo in umido con pomodorini</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sformato di pasta fillo</t>
   </si>
   <si>
+    <t xml:space="preserve">Filetto di salmone in padella al limone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamberi all'aglio e prezzemolo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Parmigiana light di zucchine</t>
   </si>
   <si>
@@ -591,157 +600,166 @@
     <t xml:space="preserve">Ingredienti (1 porzione)</t>
   </si>
   <si>
-    <t xml:space="preserve">170 g macinato magro · 1 zucchina · ½ cipolla · 110 g passata · 55 g mozzarella light · 15 g grana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 zucchine a spaghetti · 165 g macinato magro · 130 g passata · 10 g olio · spezie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 zucchine a spaghetti · 140 g pollo · 90 g pomodorini · 45 g Philadelphia light · 8 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 zucchine a spaghetti · 160 g gamberi · 90 g pomodorini · 45 g Philadelphia light · 8 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 zucchine a fette · 100 g tacchino a fette · 60 g mozzarella light · 20 g parmigiano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200 g petto di pollo · 1 zucchina · 25 g parmigiano · 1 uovo · sale e pepe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 zucchine a fette · 100 g salmone affumicato · 35 g Philadelphia light · 15 g pangrattato · 1 uovo · farina.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foglie di lattuga · 110 g fesa di tacchino · 45 g Philadelphia light · 2 uova sode.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrap: 100 g spinaci + 2 uova + 20 g parmigiano · Ripieno: 90 g salmone + 35 g Philadelphia light · Salsa: 45 g avocado + yogurt greco + limone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lattuga · cetrioli · carote · cavolo viola · 165 g pollo · 1 foglio di riso · 8 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 fogli carta di riso · 190 g gamberi · 1 uovo · aglio · spezie. Salsa: teriyaki, limone, peperoncino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210 g macinato di pollo · ⅓ carota · ⅓ cipolla · 3 fogli carta di riso · 8 g olio · spezie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 fogli carta di riso · cetriolo · carote · 150 g gamberi · insalata. Salsa: soia, burro d'arachidi, miele, lime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 fogli carta di riso · cetriolo · carote · insalata · 2 uova sode · 25 g grana. Salsa: 75 g yogurt bianco, concentrato, soia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 fogli carta di riso · ½ cipolla · 1 carota · 1 zucchina · 3 uova · spezie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g pollo · 1 zucchina · 1 carota · 100 g konjac · burro d'arachidi · soia · limone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g pollo · cipolla · zucchina · carota · farina · 10 g olio · soia · spezie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g pollo · 10 g olio · farina · succo di limone · 60 g pane integrale · insalata.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g pollo · farina · zafferano · 60 g pane integrale · insalata · 10 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g pollo · farina · 100 g champignon · 60 g pane integrale · 10 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g pollo · 130 g yogurt greco · cetriolo · limone · cipolla · 8 g olio · 40 g pane integrale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170 g macinato magro · foglie d'insalata al posto del pane · 1 sottiletta light · 2 uova.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g macinato magro · verdura di contorno · 10 g olio · 40 g pane integrale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g tonno al naturale · 110 g Philadelphia light · 30 g parmigiano · 1 uovo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190 g merluzzo · 1 uovo · 20 g pangrattato · farina · 100 g salsa di pomodoro · 8 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cetrioli · 140 g tonno al naturale · 2 uova sode · cipolla · 70 g mais. Condimento: Philadelphia, yogurt greco, limone, senape.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 g pasta fillo · zucchine · 90 g tacchino · 25 g grana · 8 g olio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 g pasta fillo · zucchine · champignon · 150 g macinato magro · parmigiano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130 g gnocchi di patate · 100 g passata · 55 g mozzarella light · 15 g parmigiano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g insalata mista · 150 g legumi in scatola sgocciolati · 80 g mais · 60 g tonno al naturale · 10 g olio EVO · succo di limone, origano.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 tacos di mais (~50 g) · 90 g gamberi sgusciati · 60 g avocado · 50 g insalata · 60 g pomodorini · 5 g olio EVO · lime, sale, peperoncino.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 tacos di mais (~50 g) · 90 g pollo · 50 g fagioli neri · 40 g mais · 40 g insalata · 30 g salsa piccante · 5 g olio · paprika, cumino, lime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 tacos di mais (~50 g) · 80 g macinato magro · 50 g fagioli rossi · 40 g pomodori · 30 g cipolla · 40 g insalata · 5 g olio · cumino, peperoncino, lime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g lattuga romana · 150 g pollo · 25 g grana a scaglie · 20 g crostini integrali. Salsa: 60 g yogurt greco, senape, limone, acciuga facoltativa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g insalata mista · 2 uova sode · 80 g tonno al naturale · 120 g fagioli cannellini · 60 g pomodorini · 10 g olio EVO · limone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g insalata mista · 150 g pollo · 60 g avocado · 60 g mais · 60 g pomodorini · 8 g olio EVO · lime.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170 g fettine di manzo magro · 60 g rucola · 30 g grana a scaglie · 10 g olio EVO · limone · 40 g pane integrale.</t>
+    <t xml:space="preserve">155 g macinato magro di manzo · 1 zucchina · 50 g cipolla · 110 g passata di pomodoro · 50 g mozzarella light · 13 g grana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175 g macinato magro di manzo · 2 zucchine · 130 g passata di pomodoro · 11 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 zucchine · 90 g pomodorini · 50 g philadelphia light · 170 g petto di pollo · 9 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 zucchine · 90 g pomodorini · 205 g gamberi · 55 g philadelphia light · 10 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 zucchine · 120 g fesa di tacchino · 75 g mozzarella light · 25 g parmigiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g petto di pollo · 1 zucchina · 25 g parmigiano · 1 uovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 zucchine · 90 g salmone affumicato · 30 g philadelphia light · 13 g pangrattato · 1 uovo · 9 g farina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione di lattuga · 145 g fesa di tacchino · 60 g philadelphia light · 2 uova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 g spinaci · 2 uova · 12 g parmigiano · 55 g salmone affumicato · 20 g philadelphia light · 30 g avocado · 20 g yogurt greco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione di lattuga · 100 g cetrioli · 60 g carote · 60 g cavolo viola · 150 g petto di pollo · 1 foglio di carta di riso · 7 g olio evo · 60 g hummus di ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 g gamberi · 3 fogli di carta di riso · 1 uovo · 20 g salsa teriyaki · 1 limone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190 g macinato di pollo · 25 g carote · 35 g cipolla · 3 fogli di carta di riso · 7 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165 g gamberi · 3 fogli di carta di riso · 100 g cetrioli · 60 g carote · 1 porzione d'insalata · 16 g burro di arachidi · 9 g miele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 uova · 3 fogli di carta di riso · 100 g cetrioli · 60 g carote · 1 porzione d'insalata · 50 g yogurt bianco · 10 g concentrato di pomodoro · 16 g grana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 fogli di carta di riso · 50 g cipolla · 80 g carote · 1 zucchina · 3 uova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185 g petto di pollo · 1 zucchina · 80 g carote · 100 g noodles di konjac · 25 g burro di arachidi · 18 ml salsa di soia · 1 limone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g petto di pollo · 40 g cipolla · 1 zucchina · 80 g carote · 10 g farina · 17 ml salsa di soia · 10 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 g petto di pollo · 9 g farina · 1 limone · 1 porzione d'insalata · 9 g olio evo · 55 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 g petto di pollo · 9 g farina · 1 bustina di zafferano · 1 porzione d'insalata · 9 g olio evo · 55 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 g petto di pollo · 9 g farina · 100 g funghi champignon · 9 g olio evo · 50 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g petto di pollo · 100 g yogurt greco · 200 g cetrioli · 40 g cipolla · 1 limone · 7 g olio evo · 75 g ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g macinato magro di manzo · 1 porzione d'insalata · 1 sottiletta light · 2 uova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165 g macinato magro di manzo · 150 g verdura di contorno · 8 g olio evo · 80 g fagioli cannellini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115 g tonno al naturale · 85 g philadelphia light · 25 g parmigiano · 1 uovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 g merluzzo · 1 uovo · 20 g pangrattato · 10 g farina · 100 g passata di pomodoro · 9 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g cetrioli · 115 g tonno al naturale · 2 uova · 40 g cipolla · 15 g mais in scatola · 10 g philadelphia light · 18 g yogurt greco · 5 g senape · 50 g fagioli cannellini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 g pasta fillo · 1 zucchina · 90 g fesa di tacchino · 25 g grana · 8 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 g pasta fillo · 1 zucchina · 80 g funghi champignon · 135 g macinato magro di manzo · 18 g parmigiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g gnocchi di patate · 100 g passata di pomodoro · 60 g mozzarella light · 18 g parmigiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione d'insalata · 150 g legumi in scatola · 80 g mais in scatola · 60 g tonno al naturale · 10 g olio evo · 1 limone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g tacos di mais · 90 g gamberi · 45 g avocado · 1 porzione d'insalata · 60 g pomodorini · 5 g olio evo · 1 lime · 50 g fagioli neri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g tacos di mais · 90 g petto di pollo · 50 g fagioli neri · 40 g mais in scatola · 1 porzione d'insalata · 30 g salsa di pomodoro piccante · 5 g olio evo · 1 lime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g tacos di mais · 80 g macinato magro di manzo · 50 g fagioli rossi · 40 g pomodori · 30 g cipolla · 1 porzione d'insalata · 5 g olio evo · 1 lime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione di lattuga · 170 g petto di pollo · 25 g grana · 60 g yogurt greco · 9 g senape · 1 limone · 70 g ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione d'insalata · 2 uova · 60 g tonno al naturale · 90 g fagioli cannellini · 60 g pomodorini · 8 g olio evo · 1 limone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione d'insalata · 160 g petto di pollo · 40 g avocado · 20 g mais in scatola · 60 g pomodorini · 7 g olio evo · 1 lime · 75 g ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130 g fettine di manzo magro · 60 g rucola · 25 g grana · 8 g olio evo · 1 limone · 30 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165 g salmone fresco · 10 g olio evo · 1 limone · 1 zucchina · 1 porzione d'insalata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 g merluzzo · 150 g pomodorini · 40 g cipolla · 12 g olio evo · 40 g pane integrale · 1 ciuffo di prezzemolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 g gamberi · 12 g olio evo · 1 spicchio d'aglio · 1 ciuffo di prezzemolo · 45 g pane integrale · 1 porzione d'insalata · 60 g pomodorini</t>
   </si>
   <si>
     <t xml:space="preserve">COLAZIONI</t>
   </si>
   <si>
-    <t xml:space="preserve">2 uova · 50 g avocado · 80 g pomodori · 40 g pane integrale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 uova · 120 g fiocchi di latte · 70 g frutti di bosco · dolcificante · cannella.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 g farina d'avena · 1 uovo + 100 g albume · 80 g fiocchi di latte · 70 g frutti di bosco · cannella.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 g ricotta light · 8 g miele · 7 g amido di mais · 5 g gocce di cioccolato · 20 g uovo sbattuto · scorza di limone. + 1 frutto (≈150 g) e 60 g fiocchi di latte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 muffin: 2 uova · 60 g spinaci · 40 g pomodorini · 25 g grana · 40 g pane integrale a parte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 g pane integrale · 60 g avocado · 1 uovo · pomodorini · sale e pepe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 g pane integrale · 1 uovo · 80 ml latte · cannella · 100 g frutti di bosco · 60 g fiocchi di latte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 g piadina integrale · 1 sottiletta light · 60 g fesa di tacchino · insalata · pomodori.</t>
+    <t xml:space="preserve">2 uova · 40 g avocado · 80 g pomodori · 35 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 uova · 150 g fiocchi di latte · 70 g frutti di bosco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 g farina d'avena · 1 uovo · 100 g albume · 60 g fiocchi di latte · 70 g frutti di bosco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 g ricotta light · 8 g miele · 7 g amido di mais · 5 g gocce di cioccolato · 20 g uovo sbattuto · 1 limone · 150 g frutta fresca · 40 g fiocchi di latte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 uova · 60 g spinaci · 40 g pomodorini · 18 g grana · 30 g pane integrale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 g pane integrale · 65 g avocado · 1 uovo · 60 g pomodorini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g pane integrale · 1 uovo · 80 ml latte · 100 g frutti di bosco · 50 g fiocchi di latte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 g piadina integrale · 1 sottiletta light · 60 g fesa di tacchino · 1 porzione d'insalata · 60 g pomodori</t>
   </si>
   <si>
     <t xml:space="preserve">MERENDE E SPUNTINI DOPO CENA</t>
   </si>
   <si>
-    <t xml:space="preserve">70 g mozzarella light · 100 g pomodori · basilico · 5 g olio EVO.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140 g fiocchi di latte · 10 g senape · 70 g carote.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈300 g di frutta estiva a scelta: melone, pesche o uva.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 g fesa di tacchino · 110 g fiocchi di latte · 80 g pomodorini.</t>
+    <t xml:space="preserve">65 g mozzarella light · 100 g pomodori · 5 g basilico · 5 g olio evo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g fiocchi di latte · 10 g senape · 70 g carote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 g frutta estiva (melone/pesche/uva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 g fesa di tacchino · 115 g fiocchi di latte · 80 g pomodorini</t>
   </si>
   <si>
     <t xml:space="preserve">Note: kcal stimate su porzione singola. Yogurt greco solo come ingrediente di salse, mai al naturale a colazione o merenda. Merenda e dopo cena usano le stesse 4 ricette, sfasate così nella stessa giornata sono diverse.</t>
@@ -774,6 +792,15 @@
     <t xml:space="preserve">200 g fiocchi di latte · 2 uova medie · 150 g spinaci freschi · 5 g olio EVO · 5 g parmigiano · sale, pepe, noce moscata. Fai appassire gli spinaci in padella con l'olio, strizzali bene e tritali. Mescolali con i fiocchi di latte, le uova sbattute, il parmigiano e le spezie. Versa in pirofila e cuoci in forno a 180 °C per 25-30 min finché è rappreso e dorato in superficie. Dosi già in linea con il pasto: nessun adattamento necessario.</t>
   </si>
   <si>
+    <t xml:space="preserve">Giant veggie roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈440 kcal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 fogli di carta di riso · foglie d'insalata · 60 g carote a julienne · 60 g cetrioli a bastoncini · 45 g avocado · 130 g petto di pollo cotto e sfilacciato. Per la salsa: 10 g burro di arachidi · 10 ml salsa di soia · 8 g miele · succo di limone. Ammorbidisci un foglio di riso alla volta in acqua tiepida, sovrapponi i tre leggermente sfalsati per ottenere una superficie unica, disponi al centro l'insalata e poi gli altri ingredienti a strisce parallele. Arrotolа stretto ripiegando prima i lati, poi taglia a metà in diagonale. Frulla o mescola gli ingredienti della salsa fino a ottenere una crema fluida, allungando con un cucchiaio d'acqua se serve. Porzioni adattate al pasto: pollo 130 g e avocado 45 g per restare in linea con le kcal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chia pudding ai frutti rossi</t>
   </si>
   <si>
@@ -822,484 +849,553 @@
     <t xml:space="preserve">420 g</t>
   </si>
   <si>
+    <t xml:space="preserve">2 pz (≈400 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">520 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carne e salumi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">515 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latticini e uova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 pz (≈273 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pane, cereali e dispensa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">625 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispensa e condimenti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">780 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSALIA — Settimana 1 (7 giorni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avocado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basilico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 pz (≈200 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutta estiva (melone/pesche/uva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutta fresca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutti di bosco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insalata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lattuga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limoni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pomodorini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinaci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdura di contorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zucchine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fesa di tacchino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macinato di pollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macinato magro di manzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">645 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petto di pollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">680 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pesce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gamberi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tonno al naturale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parmigiano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philadelphia light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricotta light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sottilette light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogurt greco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amido di mais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carta di riso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 fogli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fagioli cannellini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fagioli neri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farina d'avena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gocce di cioccolato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legumi in scatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mais in scatola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olio EVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tacos di mais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uovo sbattuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSALIA — Settimana 2 (7 giorni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 pz (≈300 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rucola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fettine di manzo magro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">940 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merluzzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burro di arachidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta fillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salsa di pomodoro piccante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salsa di soia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salsa teriyaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zafferano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 bustine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSALIA — Settimana 3 (7 giorni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cavolo viola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 porzioni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 porzione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">570 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 pz</t>
+  </si>
+  <si>
     <t xml:space="preserve">400 g</t>
   </si>
   <si>
-    <t xml:space="preserve">80 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 porzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carne e salumi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">515 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latticini e uova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 pz (≈295 g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pane, cereali e dispensa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">625 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dispensa e condimenti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">780 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSALIA — Settimana 1 (7 giorni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avocado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basilico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385 g</t>
+    <t xml:space="preserve">530 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmone affumicato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 pz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogurt bianco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 fogli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrato di pomodoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fagioli rossi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hummus di ceci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noodles di konjac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69 g</t>
   </si>
   <si>
     <t xml:space="preserve">200 g</t>
   </si>
   <si>
-    <t xml:space="preserve">175 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutta estiva (melone/pesche/uva)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">900 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutta fresca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutti di bosco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">240 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insalata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 porzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lattuga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 porzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limoni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pomodorini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">480 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinaci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verdura di contorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zucchine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fesa di tacchino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macinato di pollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macinato magro di manzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">685 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petto di pollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pesce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gamberi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonno al naturale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80 ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parmigiano</t>
+    <t xml:space="preserve">13 g</t>
   </si>
   <si>
     <t xml:space="preserve">40 g</t>
   </si>
   <si>
-    <t xml:space="preserve">Philadelphia light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricotta light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sottilette light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yogurt greco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amido di mais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carta di riso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 fogli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farina d'avena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gocce di cioccolato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legumi in scatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mais in scatola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olio EVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tacos di mais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSALIA — Settimana 2 (7 giorni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 porzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rucola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fettine di manzo magro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">920 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merluzzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burro di arachidi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fagioli cannellini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fagioli neri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta fillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salsa di pomodoro piccante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salsa di soia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salsa teriyaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zafferano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 bustine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSALIA — Settimana 3 (7 giorni)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cavolo viola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 porzioni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 porzione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 pz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">360 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">580 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salmone affumicato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yogurt bianco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 fogli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrato di pomodoro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fagioli rossi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noodles di konjac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64 g</t>
+    <t xml:space="preserve">Prezzemolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmone fresco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 ml</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1410,7 @@
   <fonts count="13">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1832,193 +1928,18 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1f497d"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="eeece1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4f81bd"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="c0504d"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9bbb59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064a2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4bacc6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="f79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ff"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E169"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
   </cols>
   <sheetData>
@@ -2727,7 +2648,7 @@
       <c r="D50" s="4"/>
       <c r="E50" s="5" t="n">
         <f aca="false">E72</f>
-        <v>1703.46</v>
+        <v>1700.3</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2849,11 +2770,11 @@
         <v>30</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E58" s="11" t="n">
         <f aca="false">C58*D58/100</f>
-        <v>39</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3003,14 +2924,14 @@
         <v>25</v>
       </c>
       <c r="C68" s="10" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>353</v>
       </c>
       <c r="E68" s="11" t="n">
         <f aca="false">C68*D68/100</f>
-        <v>254.16</v>
+        <v>247.1</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3070,7 +2991,7 @@
       </c>
       <c r="E72" s="19" t="n">
         <f aca="false">SUM(E52:E71)</f>
-        <v>1703.46</v>
+        <v>1700.3</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3082,7 +3003,7 @@
       <c r="D74" s="4"/>
       <c r="E74" s="5" t="n">
         <f aca="false">E95</f>
-        <v>1703.9</v>
+        <v>1702.6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3342,14 +3263,14 @@
         <v>58</v>
       </c>
       <c r="C91" s="10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D91" s="10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E91" s="11" t="n">
         <f aca="false">C91*D91/100</f>
-        <v>130</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3409,7 +3330,7 @@
       </c>
       <c r="E95" s="19" t="n">
         <f aca="false">SUM(E76:E94)</f>
-        <v>1703.9</v>
+        <v>1702.6</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3421,7 +3342,7 @@
       <c r="D97" s="4"/>
       <c r="E97" s="5" t="n">
         <f aca="false">E118</f>
-        <v>1700.85</v>
+        <v>1701.89</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3524,14 +3445,14 @@
         <v>61</v>
       </c>
       <c r="C104" s="10" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E104" s="11" t="n">
         <f aca="false">C104*D104/100</f>
-        <v>182</v>
+        <v>183.04</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3748,7 +3669,7 @@
       </c>
       <c r="E118" s="19" t="n">
         <f aca="false">SUM(E99:E117)</f>
-        <v>1700.85</v>
+        <v>1701.89</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4083,7 +4004,7 @@
       <c r="D142" s="4"/>
       <c r="E142" s="5" t="n">
         <f aca="false">E163</f>
-        <v>1700.9</v>
+        <v>1704.15</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4346,11 +4267,11 @@
         <v>25</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E159" s="11" t="n">
         <f aca="false">C159*D159/100</f>
-        <v>32.5</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4410,7 +4331,7 @@
       </c>
       <c r="E163" s="19" t="n">
         <f aca="false">SUM(E144:E162)</f>
-        <v>1700.9</v>
+        <v>1704.15</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4504,16 +4425,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="95.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4712,15 +4633,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C157"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
   </cols>
   <sheetData>
@@ -4752,7 +4673,7 @@
       <c r="B5" s="29"/>
       <c r="C5" s="30" t="n">
         <f aca="false">SUM(C6:C10)</f>
-        <v>1545</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4774,7 +4695,7 @@
         <v>128</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4785,7 +4706,7 @@
         <v>129</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4796,7 +4717,7 @@
         <v>130</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4807,7 +4728,7 @@
         <v>132</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4817,7 +4738,7 @@
       <c r="B12" s="29"/>
       <c r="C12" s="30" t="n">
         <f aca="false">SUM(C13:C17)</f>
-        <v>1535</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4828,7 +4749,7 @@
         <v>134</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4839,7 +4760,7 @@
         <v>135</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4850,7 +4771,7 @@
         <v>136</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4861,7 +4782,7 @@
         <v>137</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4882,7 +4803,7 @@
       <c r="B19" s="29"/>
       <c r="C19" s="30" t="n">
         <f aca="false">SUM(C20:C24)</f>
-        <v>1540</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4893,7 +4814,7 @@
         <v>140</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4904,7 +4825,7 @@
         <v>141</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4915,7 +4836,7 @@
         <v>132</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4926,7 +4847,7 @@
         <v>142</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4937,7 +4858,7 @@
         <v>129</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4947,7 +4868,7 @@
       <c r="B26" s="29"/>
       <c r="C26" s="30" t="n">
         <f aca="false">SUM(C27:C31)</f>
-        <v>1560</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4969,7 +4890,7 @@
         <v>145</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5002,7 +4923,7 @@
         <v>136</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5012,7 +4933,7 @@
       <c r="B33" s="29"/>
       <c r="C33" s="30" t="n">
         <f aca="false">SUM(C34:C38)</f>
-        <v>1540</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5034,7 +4955,7 @@
         <v>149</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5045,7 +4966,7 @@
         <v>129</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5056,7 +4977,7 @@
         <v>150</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>425</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5067,7 +4988,7 @@
         <v>132</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5077,7 +4998,7 @@
       <c r="B40" s="29"/>
       <c r="C40" s="30" t="n">
         <f aca="false">SUM(C41:C45)</f>
-        <v>1550</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,7 +5020,7 @@
         <v>153</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5110,7 +5031,7 @@
         <v>136</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5121,7 +5042,7 @@
         <v>115</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5142,7 +5063,7 @@
       <c r="B47" s="29"/>
       <c r="C47" s="30" t="n">
         <f aca="false">SUM(C48:C52)</f>
-        <v>1535</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5164,7 +5085,7 @@
         <v>156</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,7 +5096,7 @@
         <v>132</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5186,7 +5107,7 @@
         <v>157</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,7 +5118,7 @@
         <v>129</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5214,7 +5135,7 @@
       <c r="B56" s="29"/>
       <c r="C56" s="30" t="n">
         <f aca="false">SUM(C57:C61)</f>
-        <v>1545</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5225,7 +5146,7 @@
         <v>159</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,7 +5157,7 @@
         <v>160</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5258,7 +5179,7 @@
         <v>161</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5269,7 +5190,7 @@
         <v>136</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,7 +5200,7 @@
       <c r="B63" s="29"/>
       <c r="C63" s="30" t="n">
         <f aca="false">SUM(C64:C68)</f>
-        <v>1535</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5301,7 +5222,7 @@
         <v>162</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5312,7 +5233,7 @@
         <v>129</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,7 +5244,7 @@
         <v>163</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5334,7 +5255,7 @@
         <v>132</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5344,7 +5265,7 @@
       <c r="B70" s="29"/>
       <c r="C70" s="30" t="n">
         <f aca="false">SUM(C71:C75)</f>
-        <v>1535</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5355,7 +5276,7 @@
         <v>134</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5366,7 +5287,7 @@
         <v>164</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5377,7 +5298,7 @@
         <v>136</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5388,7 +5309,7 @@
         <v>165</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5409,7 +5330,7 @@
       <c r="B77" s="29"/>
       <c r="C77" s="30" t="n">
         <f aca="false">SUM(C78:C82)</f>
-        <v>1545</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5420,7 +5341,7 @@
         <v>140</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5431,7 +5352,7 @@
         <v>166</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,7 +5363,7 @@
         <v>132</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5453,7 +5374,7 @@
         <v>167</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5464,7 +5385,7 @@
         <v>129</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5474,7 +5395,7 @@
       <c r="B84" s="29"/>
       <c r="C84" s="30" t="n">
         <f aca="false">SUM(C85:C89)</f>
-        <v>1535</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5496,7 +5417,7 @@
         <v>168</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5518,7 +5439,7 @@
         <v>169</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5529,7 +5450,7 @@
         <v>136</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5539,7 +5460,7 @@
       <c r="B91" s="29"/>
       <c r="C91" s="30" t="n">
         <f aca="false">SUM(C92:C96)</f>
-        <v>1550</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,7 +5482,7 @@
         <v>170</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5572,7 +5493,7 @@
         <v>129</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5583,7 +5504,7 @@
         <v>171</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5594,7 +5515,7 @@
         <v>132</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,7 +5525,7 @@
       <c r="B98" s="29"/>
       <c r="C98" s="30" t="n">
         <f aca="false">SUM(C99:C103)</f>
-        <v>1550</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5626,7 +5547,7 @@
         <v>172</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5637,7 +5558,7 @@
         <v>136</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5676,7 +5597,7 @@
       <c r="B107" s="29"/>
       <c r="C107" s="30" t="n">
         <f aca="false">SUM(C108:C112)</f>
-        <v>1540</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5698,7 +5619,7 @@
         <v>175</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5709,7 +5630,7 @@
         <v>132</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,7 +5641,7 @@
         <v>176</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5731,7 +5652,7 @@
         <v>129</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5741,7 +5662,7 @@
       <c r="B114" s="29"/>
       <c r="C114" s="30" t="n">
         <f aca="false">SUM(C115:C119)</f>
-        <v>1540</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5752,7 +5673,7 @@
         <v>159</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5763,7 +5684,7 @@
         <v>177</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5785,7 +5706,7 @@
         <v>178</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5796,7 +5717,7 @@
         <v>136</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5806,7 +5727,7 @@
       <c r="B121" s="29"/>
       <c r="C121" s="30" t="n">
         <f aca="false">SUM(C122:C126)</f>
-        <v>1545</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5828,7 +5749,7 @@
         <v>179</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5839,7 +5760,7 @@
         <v>129</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5847,7 +5768,7 @@
         <v>23</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C125" s="11" t="n">
         <v>435</v>
@@ -5861,7 +5782,7 @@
         <v>132</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5871,7 +5792,7 @@
       <c r="B128" s="29"/>
       <c r="C128" s="30" t="n">
         <f aca="false">SUM(C129:C133)</f>
-        <v>1555</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5882,7 +5803,7 @@
         <v>134</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5893,7 +5814,7 @@
         <v>180</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5904,7 +5825,7 @@
         <v>136</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5915,7 +5836,7 @@
         <v>157</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5936,7 +5857,7 @@
       <c r="B135" s="29"/>
       <c r="C135" s="30" t="n">
         <f aca="false">SUM(C136:C140)</f>
-        <v>1565</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5947,7 +5868,7 @@
         <v>140</v>
       </c>
       <c r="C136" s="11" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5958,7 +5879,7 @@
         <v>181</v>
       </c>
       <c r="C137" s="11" t="n">
-        <v>445</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5969,7 +5890,7 @@
         <v>132</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5977,7 +5898,7 @@
         <v>23</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="C139" s="11" t="n">
         <v>430</v>
@@ -5991,7 +5912,7 @@
         <v>129</v>
       </c>
       <c r="C140" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6001,7 +5922,7 @@
       <c r="B142" s="29"/>
       <c r="C142" s="30" t="n">
         <f aca="false">SUM(C143:C147)</f>
-        <v>1545</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6020,10 +5941,10 @@
         <v>13</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6042,10 +5963,10 @@
         <v>23</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6056,7 +5977,7 @@
         <v>136</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6066,7 +5987,7 @@
       <c r="B149" s="29"/>
       <c r="C149" s="30" t="n">
         <f aca="false">SUM(C150:C154)</f>
-        <v>1545</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6085,7 +6006,7 @@
         <v>13</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C151" s="11" t="n">
         <v>435</v>
@@ -6099,7 +6020,7 @@
         <v>129</v>
       </c>
       <c r="C152" s="11" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6107,10 +6028,10 @@
         <v>23</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6121,17 +6042,17 @@
         <v>132</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B157" s="35"/>
       <c r="C157" s="36" t="n">
         <f aca="false">AVERAGE(C5,C12,C19,C26,C33,C40,C47,C56,C63,C70,C77,C84,C91,C98,C107,C114,C121,C128,C135,C142,C149)</f>
-        <v>1544.52380952381</v>
+        <v>1546.90476190476</v>
       </c>
     </row>
   </sheetData>
@@ -6175,28 +6096,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C64"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="87.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -6209,7 +6130,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6217,10 +6138,10 @@
         <v>130</v>
       </c>
       <c r="B5" s="11" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6228,10 +6149,10 @@
         <v>142</v>
       </c>
       <c r="B6" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6239,10 +6160,10 @@
         <v>168</v>
       </c>
       <c r="B7" s="11" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6250,21 +6171,21 @@
         <v>164</v>
       </c>
       <c r="B8" s="11" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B9" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6275,7 +6196,7 @@
         <v>435</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6283,10 +6204,10 @@
         <v>178</v>
       </c>
       <c r="B11" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6294,10 +6215,10 @@
         <v>156</v>
       </c>
       <c r="B12" s="11" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6305,10 +6226,10 @@
         <v>180</v>
       </c>
       <c r="B13" s="11" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6316,10 +6237,10 @@
         <v>175</v>
       </c>
       <c r="B14" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6327,10 +6248,10 @@
         <v>172</v>
       </c>
       <c r="B15" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6338,10 +6259,10 @@
         <v>145</v>
       </c>
       <c r="B16" s="11" t="n">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6349,10 +6270,10 @@
         <v>166</v>
       </c>
       <c r="B17" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6360,10 +6281,10 @@
         <v>177</v>
       </c>
       <c r="B18" s="11" t="n">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6371,10 +6292,10 @@
         <v>150</v>
       </c>
       <c r="B19" s="11" t="n">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6382,10 +6303,10 @@
         <v>179</v>
       </c>
       <c r="B20" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6393,10 +6314,10 @@
         <v>171</v>
       </c>
       <c r="B21" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6404,10 +6325,10 @@
         <v>161</v>
       </c>
       <c r="B22" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6415,10 +6336,10 @@
         <v>167</v>
       </c>
       <c r="B23" s="11" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6426,10 +6347,10 @@
         <v>137</v>
       </c>
       <c r="B24" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6437,10 +6358,10 @@
         <v>128</v>
       </c>
       <c r="B25" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6448,10 +6369,10 @@
         <v>141</v>
       </c>
       <c r="B26" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6459,10 +6380,10 @@
         <v>157</v>
       </c>
       <c r="B27" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6470,10 +6391,10 @@
         <v>176</v>
       </c>
       <c r="B28" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6481,10 +6402,10 @@
         <v>163</v>
       </c>
       <c r="B29" s="11" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6492,10 +6413,10 @@
         <v>160</v>
       </c>
       <c r="B30" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6503,21 +6424,21 @@
         <v>169</v>
       </c>
       <c r="B31" s="11" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B32" s="11" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6525,10 +6446,10 @@
         <v>115</v>
       </c>
       <c r="B33" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6536,10 +6457,10 @@
         <v>135</v>
       </c>
       <c r="B34" s="11" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6547,10 +6468,10 @@
         <v>149</v>
       </c>
       <c r="B35" s="11" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6558,10 +6479,10 @@
         <v>170</v>
       </c>
       <c r="B36" s="11" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6569,10 +6490,10 @@
         <v>181</v>
       </c>
       <c r="B37" s="11" t="n">
-        <v>445</v>
+        <v>410</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6580,10 +6501,10 @@
         <v>153</v>
       </c>
       <c r="B38" s="11" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6591,10 +6512,10 @@
         <v>162</v>
       </c>
       <c r="B39" s="11" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6605,7 +6526,7 @@
         <v>435</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6613,194 +6534,227 @@
         <v>165</v>
       </c>
       <c r="B41" s="11" t="n">
+        <v>440</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>435</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="11" t="n">
         <v>430</v>
       </c>
-      <c r="C41" s="40" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="C43" s="40" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>435</v>
+      </c>
+      <c r="C44" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>330</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>330</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>335</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>228</v>
+      <c r="C47" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="39" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>330</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="39" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B49" s="11" t="n">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="39" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B50" s="11" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="39" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B51" s="11" t="n">
         <v>330</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>330</v>
+      </c>
+      <c r="C52" s="40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>335</v>
+      </c>
+      <c r="C53" s="40" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>330</v>
+      </c>
+      <c r="C54" s="40" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="B52" s="11" t="n">
-        <v>335</v>
-      </c>
-      <c r="C52" s="40" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="B55" s="11" t="n">
+        <v>340</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B58" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>175</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>175</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>237</v>
+      <c r="C58" s="7" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="39" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B59" s="11" t="n">
         <v>180</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="41" t="s">
-        <v>239</v>
-      </c>
-      <c r="B61" s="41"/>
-      <c r="C61" s="41"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>185</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>190</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" s="41"/>
+      <c r="C64" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6813,28 +6767,28 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="126.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="42" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6844,7 +6798,7 @@
         <v>76</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>78</v>
@@ -6852,82 +6806,93 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
     </row>
     <row r="6" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>225</v>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-    </row>
-    <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>251</v>
-      </c>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="99.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>258</v>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -6935,7 +6900,7 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6948,12 +6913,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B223"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B235"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -6961,25 +6926,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B1" s="44"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B4" s="45"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B5" s="7"/>
     </row>
@@ -6988,7 +6953,7 @@
         <v>51</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6996,7 +6961,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7004,7 +6969,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7012,7 +6977,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7020,7 +6985,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7028,7 +6993,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7036,7 +7001,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7044,12 +7009,12 @@
         <v>28</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B14" s="7"/>
     </row>
@@ -7058,7 +7023,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7066,7 +7031,7 @@
         <v>54</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7074,7 +7039,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7082,7 +7047,7 @@
         <v>40</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7090,12 +7055,12 @@
         <v>50</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B20" s="7"/>
     </row>
@@ -7104,7 +7069,7 @@
         <v>37</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7112,7 +7077,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7120,7 +7085,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7128,15 +7093,15 @@
         <v>56</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7144,12 +7109,12 @@
         <v>21</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B27" s="7"/>
     </row>
@@ -7158,7 +7123,7 @@
         <v>55</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7166,7 +7131,7 @@
         <v>31</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7174,7 +7139,7 @@
         <v>66</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7182,7 +7147,7 @@
         <v>48</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7190,7 +7155,7 @@
         <v>43</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,7 +7163,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7206,7 +7171,7 @@
         <v>45</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7214,7 +7179,7 @@
         <v>25</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7222,7 +7187,7 @@
         <v>53</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7230,12 +7195,12 @@
         <v>39</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B38" s="7"/>
     </row>
@@ -7244,7 +7209,7 @@
         <v>36</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7252,7 +7217,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="47" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7260,7 +7225,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7268,7 +7233,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7276,7 +7241,7 @@
         <v>18</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7284,43 +7249,43 @@
         <v>26</v>
       </c>
       <c r="B44" s="47" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="48" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B46" s="48"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="46" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B49" s="47" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7328,7 +7293,7 @@
         <v>19</v>
       </c>
       <c r="B51" s="47" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7336,31 +7301,31 @@
         <v>17</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="46" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="46" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7368,39 +7333,39 @@
         <v>35</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="46" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B57" s="47" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="46" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B59" s="47" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7408,113 +7373,113 @@
         <v>41</v>
       </c>
       <c r="B61" s="47" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="46" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B63" s="47" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="46" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B65" s="47" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="46" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B68" s="47" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="46" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="46" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B73" s="47" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7522,23 +7487,23 @@
         <v>37</v>
       </c>
       <c r="B76" s="47" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="46" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B78" s="47" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7546,427 +7511,427 @@
         <v>56</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>278</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="46" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B80" s="47" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="46" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B82" s="47" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="46" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B84" s="47" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="46" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B88" s="47" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>36</v>
+        <v>366</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="46" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B90" s="47" t="s">
-        <v>346</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>66</v>
+        <v>369</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="46" t="s">
-        <v>360</v>
+        <v>36</v>
       </c>
       <c r="B92" s="47" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>267</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="46" t="s">
-        <v>363</v>
+        <v>66</v>
       </c>
       <c r="B94" s="47" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="46" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B96" s="47" t="s">
-        <v>367</v>
+        <v>276</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>9</v>
+        <v>377</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>368</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="46" t="s">
-        <v>26</v>
+        <v>378</v>
       </c>
       <c r="B98" s="47" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="46" t="s">
-        <v>372</v>
+        <v>9</v>
       </c>
       <c r="B100" s="47" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="48" t="s">
-        <v>373</v>
-      </c>
-      <c r="B102" s="48"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="B102" s="47" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B103" s="7"/>
+      <c r="A103" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="46" t="s">
-        <v>301</v>
-      </c>
-      <c r="B105" s="47" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>368</v>
-      </c>
+      <c r="A104" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="B104" s="47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="B106" s="48"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B107" s="47" t="s">
-        <v>374</v>
-      </c>
+      <c r="A107" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B107" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="9" t="s">
-        <v>17</v>
+        <v>308</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B109" s="47" t="s">
-        <v>375</v>
+        <v>302</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>267</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="46" t="s">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="B111" s="47" t="s">
-        <v>272</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
-        <v>313</v>
+        <v>17</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B113" s="47" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="46" t="s">
-        <v>41</v>
+        <v>318</v>
       </c>
       <c r="B115" s="47" t="s">
-        <v>378</v>
+        <v>281</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="46" t="s">
-        <v>380</v>
+        <v>325</v>
       </c>
       <c r="B117" s="47" t="s">
-        <v>294</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="46" t="s">
-        <v>326</v>
+        <v>41</v>
       </c>
       <c r="B119" s="47" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B120" s="7"/>
+      <c r="A120" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>374</v>
+      <c r="A121" s="46" t="s">
+        <v>395</v>
+      </c>
+      <c r="B121" s="47" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="46" t="s">
-        <v>382</v>
-      </c>
-      <c r="B122" s="47" t="s">
-        <v>300</v>
+      <c r="A122" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="9" t="s">
+      <c r="A123" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>383</v>
+      <c r="B123" s="47" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="B124" s="7"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="46" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B126" s="47" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="9" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>286</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="B128" s="7"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="9" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>312</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="46" t="s">
-        <v>37</v>
+        <v>402</v>
       </c>
       <c r="B130" s="47" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="9" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="B132" s="47" t="s">
-        <v>386</v>
-      </c>
+      <c r="A132" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="9" t="s">
         <v>347</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="46" t="s">
-        <v>348</v>
+        <v>37</v>
       </c>
       <c r="B134" s="47" t="s">
-        <v>285</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7974,273 +7939,273 @@
         <v>349</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="46" t="s">
-        <v>281</v>
+        <v>56</v>
       </c>
       <c r="B136" s="47" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>346</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B138" s="7"/>
+      <c r="A138" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B138" s="47" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="9" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="46" t="s">
-        <v>388</v>
+        <v>290</v>
       </c>
       <c r="B140" s="47" t="s">
-        <v>302</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="9" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="46" t="s">
-        <v>389</v>
-      </c>
-      <c r="B142" s="47" t="s">
-        <v>390</v>
-      </c>
+      <c r="A142" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="9" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="46" t="s">
-        <v>36</v>
+        <v>410</v>
       </c>
       <c r="B144" s="47" t="s">
-        <v>346</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="9" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="46" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B146" s="47" t="s">
-        <v>361</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="9" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B148" s="47" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="9" t="s">
-        <v>366</v>
+        <v>36</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="46" t="s">
-        <v>9</v>
+        <v>372</v>
       </c>
       <c r="B150" s="47" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="9" t="s">
-        <v>45</v>
+        <v>374</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="46" t="s">
-        <v>26</v>
+        <v>377</v>
       </c>
       <c r="B152" s="47" t="s">
-        <v>312</v>
+        <v>412</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="9" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>276</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="46" t="s">
-        <v>53</v>
+        <v>380</v>
       </c>
       <c r="B154" s="47" t="s">
-        <v>280</v>
+        <v>415</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="9" t="s">
-        <v>396</v>
+        <v>9</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="46" t="s">
-        <v>398</v>
+        <v>45</v>
       </c>
       <c r="B156" s="47" t="s">
-        <v>399</v>
+        <v>302</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="9" t="s">
-        <v>400</v>
+        <v>26</v>
       </c>
       <c r="B157" s="10" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="46" t="s">
-        <v>370</v>
+        <v>416</v>
       </c>
       <c r="B158" s="47" t="s">
-        <v>346</v>
+        <v>285</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="9" t="s">
-        <v>372</v>
+        <v>53</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>371</v>
+        <v>289</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="46" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="B160" s="47" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="48" t="s">
-        <v>403</v>
-      </c>
-      <c r="B162" s="48"/>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="B162" s="47" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B163" s="7"/>
+      <c r="A163" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>404</v>
+      <c r="A164" s="46" t="s">
+        <v>385</v>
+      </c>
+      <c r="B164" s="47" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="46" t="s">
-        <v>301</v>
-      </c>
-      <c r="B165" s="47" t="s">
+      <c r="A165" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="B165" s="10" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="46" t="s">
-        <v>405</v>
-      </c>
-      <c r="B167" s="47" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B168" s="10" t="s">
-        <v>265</v>
-      </c>
+      <c r="A166" s="46" t="s">
+        <v>422</v>
+      </c>
+      <c r="B166" s="47" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="B168" s="48"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="B169" s="47" t="s">
-        <v>390</v>
-      </c>
+      <c r="A169" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B169" s="7"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8248,241 +8213,241 @@
         <v>309</v>
       </c>
       <c r="B171" s="47" t="s">
-        <v>267</v>
+        <v>310</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="46" t="s">
-        <v>35</v>
+        <v>425</v>
       </c>
       <c r="B173" s="47" t="s">
-        <v>406</v>
+        <v>303</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B174" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="B174" s="10" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="46" t="s">
-        <v>315</v>
+        <v>17</v>
       </c>
       <c r="B175" s="47" t="s">
-        <v>408</v>
+        <v>289</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B176" s="10" t="s">
-        <v>377</v>
+        <v>316</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="46" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B177" s="47" t="s">
-        <v>409</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="9" t="s">
-        <v>41</v>
+        <v>318</v>
       </c>
       <c r="B178" s="10" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="46" t="s">
-        <v>322</v>
+        <v>35</v>
       </c>
       <c r="B179" s="47" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B180" s="10" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B181" s="47" t="s">
-        <v>267</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B182" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B182" s="10" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="B183" s="7"/>
+      <c r="A183" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="B183" s="47" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="9" t="s">
-        <v>328</v>
+        <v>41</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>412</v>
+        <v>331</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="46" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B185" s="47" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>414</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B187" s="7"/>
+      <c r="A187" s="46" t="s">
+        <v>333</v>
+      </c>
+      <c r="B187" s="47" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="9" t="s">
-        <v>415</v>
+        <v>334</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>352</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="B189" s="47" t="s">
-        <v>267</v>
-      </c>
+      <c r="A189" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B190" s="7"/>
+      <c r="A190" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="B191" s="10" t="s">
-        <v>312</v>
+      <c r="A191" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="B191" s="47" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B192" s="47" t="s">
-        <v>340</v>
+      <c r="A192" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>342</v>
-      </c>
+      <c r="A193" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B193" s="7"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="B194" s="47" t="s">
-        <v>344</v>
+      <c r="A194" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>416</v>
+      <c r="A195" s="46" t="s">
+        <v>402</v>
+      </c>
+      <c r="B195" s="47" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="B196" s="47" t="s">
-        <v>285</v>
+      <c r="A196" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="B197" s="10" t="s">
-        <v>406</v>
+      <c r="A197" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="B197" s="47" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="46" t="s">
-        <v>348</v>
-      </c>
-      <c r="B198" s="47" t="s">
-        <v>285</v>
-      </c>
+      <c r="A198" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B198" s="7"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="9" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="46" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="B200" s="47" t="s">
-        <v>387</v>
+        <v>348</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="9" t="s">
-        <v>417</v>
+        <v>349</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8490,173 +8455,269 @@
         <v>351</v>
       </c>
       <c r="B202" s="47" t="s">
-        <v>410</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="B203" s="7"/>
+      <c r="A203" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B204" s="10" t="s">
+      <c r="A204" s="46" t="s">
         <v>354</v>
       </c>
+      <c r="B204" s="47" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="46" t="s">
-        <v>388</v>
-      </c>
-      <c r="B205" s="47" t="s">
-        <v>419</v>
+      <c r="A205" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="B206" s="10" t="s">
-        <v>420</v>
+      <c r="A206" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B206" s="47" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="B207" s="47" t="s">
+      <c r="A207" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="46" t="s">
+        <v>290</v>
+      </c>
+      <c r="B208" s="47" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="B210" s="47" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="B209" s="47" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>346</v>
-      </c>
-    </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="B211" s="47" t="s">
-        <v>361</v>
-      </c>
+      <c r="A211" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="9" t="s">
-        <v>363</v>
+        <v>440</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>294</v>
+        <v>441</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="46" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B213" s="47" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="9" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="46" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B215" s="47" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="9" t="s">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="46" t="s">
-        <v>45</v>
+        <v>368</v>
       </c>
       <c r="B217" s="47" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="9" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>296</v>
+        <v>370</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="46" t="s">
-        <v>395</v>
+        <v>36</v>
       </c>
       <c r="B219" s="47" t="s">
-        <v>276</v>
+        <v>371</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="9" t="s">
-        <v>53</v>
+        <v>372</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>280</v>
+        <v>373</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="46" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="B221" s="47" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="9" t="s">
-        <v>370</v>
+        <v>446</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>346</v>
+        <v>303</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="46" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B223" s="47" t="s">
-        <v>371</v>
+        <v>379</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="B225" s="47" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B227" s="47" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="B229" s="47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="46" t="s">
+        <v>454</v>
+      </c>
+      <c r="B231" s="47" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="B233" s="47" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="B235" s="47" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -8675,18 +8736,18 @@
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A107:B107"/>
     <mergeCell ref="A124:B124"/>
     <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A138:B138"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="A183:B183"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="A190:B190"/>
-    <mergeCell ref="A203:B203"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="A211:B211"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
